--- a/data/rec_patterns/2000_kcal_patterns.xlsx
+++ b/data/rec_patterns/2000_kcal_patterns.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmb73/Library/CloudStorage/Box-Box/project_human_cost/paper_fl_risk_diets/data/diets/DGA 2020-2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bmb73/Documents/GitHub/forced-labor/data/rec_patterns/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912ECAD6-BAF8-DC4A-8679-A27FA196310E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5681D114-A8E9-7945-B9FF-C8BE52FD06EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19520" xr2:uid="{784ED3A3-12CD-EB44-8C9F-39E5523AF868}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{784ED3A3-12CD-EB44-8C9F-39E5523AF868}"/>
   </bookViews>
   <sheets>
     <sheet name="DGA Patterns" sheetId="1" r:id="rId1"/>
     <sheet name="EAT-Lancet Pattern" sheetId="7" r:id="rId2"/>
-    <sheet name="Fruit proportions" sheetId="4" r:id="rId3"/>
-    <sheet name="Animal protein props US MED" sheetId="5" r:id="rId4"/>
-    <sheet name="Veg protein proportions US MED" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="60">
   <si>
     <t>Food_Groups</t>
   </si>
@@ -105,18 +102,12 @@
     <t>Eggs</t>
   </si>
   <si>
-    <t>food</t>
-  </si>
-  <si>
     <t>gr_refined</t>
   </si>
   <si>
     <t>gr_whole</t>
   </si>
   <si>
-    <t>fruit</t>
-  </si>
-  <si>
     <t>fruit_exc_juice</t>
   </si>
   <si>
@@ -147,12 +138,6 @@
     <t>pf_egg</t>
   </si>
   <si>
-    <t>pf_poultry</t>
-  </si>
-  <si>
-    <t>pf_redm</t>
-  </si>
-  <si>
     <t>pf_seafood</t>
   </si>
   <si>
@@ -163,33 +148,6 @@
   </si>
   <si>
     <t>sat_fat</t>
-  </si>
-  <si>
-    <t>pf_animal</t>
-  </si>
-  <si>
-    <t>pf_plant</t>
-  </si>
-  <si>
-    <t>daily_intake_cups</t>
-  </si>
-  <si>
-    <t>fruit_proportion</t>
-  </si>
-  <si>
-    <t>US_VEG_CF_cups</t>
-  </si>
-  <si>
-    <t>MED_CF_cups</t>
-  </si>
-  <si>
-    <t>daily_intake_oz</t>
-  </si>
-  <si>
-    <t>protein_proportion</t>
-  </si>
-  <si>
-    <t>US_MED_CF_oz</t>
   </si>
   <si>
     <t>Fruit Juice</t>
@@ -285,18 +243,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -311,14 +263,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,31 +598,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>61</v>
+      <c r="J1" s="3" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -680,27 +630,27 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="3">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2">
         <f>1.5/7</f>
         <v>0.21428571428571427</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <f>1.5/7</f>
         <v>0.21428571428571427</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <f>1.5/7</f>
         <v>0.21428571428571427</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>0.32</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>0.32</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>0.32</v>
       </c>
       <c r="I2" t="s">
@@ -712,27 +662,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="3">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2">
         <f>5.5/7</f>
         <v>0.7857142857142857</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <f>5.5/7</f>
         <v>0.7857142857142857</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <f>5.5/7</f>
         <v>0.7857142857142857</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>0.93</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>0.93</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>0.93</v>
       </c>
       <c r="I3" t="s">
@@ -744,27 +694,27 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="3">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2">
         <f>5/7</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <f>5/7</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <f>5/7</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>0.93</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>0.93</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>0.93</v>
       </c>
       <c r="I4" t="s">
@@ -776,27 +726,27 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
         <f>4/7</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <f>4/7</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <f>4/7</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>0.75</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>0.75</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>0.75</v>
       </c>
       <c r="I5" t="s">
@@ -805,27 +755,27 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="3">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2">
         <v>1.54</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>1.92</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>1.54</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>1.51</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>1.88</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>1.51</v>
       </c>
       <c r="I6" t="s">
@@ -834,27 +784,27 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="3">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2">
         <v>0.46</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>0.57999999999999996</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>0.46</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>0.49</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>0.62</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>0.49</v>
       </c>
       <c r="I7" t="s">
@@ -866,24 +816,24 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
         <v>3.5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>4.25</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="2">
         <v>4.25</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="2">
         <v>4.75</v>
       </c>
       <c r="I8" t="s">
@@ -895,24 +845,24 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C9" s="3">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>3</v>
+      </c>
+      <c r="F9" s="2">
         <v>4.25</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>4.25</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>4.25</v>
       </c>
       <c r="I9" t="s">
@@ -924,24 +874,24 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3</v>
-      </c>
-      <c r="D10" s="3">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" s="3">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2">
         <v>2.5</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>3</v>
       </c>
       <c r="I10" t="s">
@@ -953,24 +903,24 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="3">
+        <v>55</v>
+      </c>
+      <c r="C11" s="2">
         <v>1.77</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>1.77</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>0</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>1.85</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>1.85</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>0</v>
       </c>
       <c r="I11" t="s">
@@ -982,24 +932,24 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="3">
+        <v>56</v>
+      </c>
+      <c r="C12" s="2">
         <v>1.46</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>1.46</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>0</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>1.87</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>1.87</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>0</v>
       </c>
       <c r="I12" t="s">
@@ -1011,25 +961,25 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="3">
+        <v>32</v>
+      </c>
+      <c r="C13" s="2">
         <v>0.48</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>0.48</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <f>3/7</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>0.7</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>0.7</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>0.43</v>
       </c>
       <c r="I13" t="s">
@@ -1041,26 +991,26 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="3">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2">
         <f>8/7</f>
         <v>1.1428571428571428</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <f>15/7</f>
         <v>2.1428571428571428</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>1.43</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>2.36</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>0</v>
       </c>
       <c r="I14" t="s">
@@ -1069,28 +1019,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="3">
+        <v>29</v>
+      </c>
+      <c r="C15" s="2">
         <v>0.63</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>0.63</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="2">
         <f>1/1</f>
         <v>1</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>0.63</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="2">
         <v>0.63</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>1.21</v>
       </c>
       <c r="I15" t="s">
@@ -1099,28 +1049,28 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="3">
+        <v>30</v>
+      </c>
+      <c r="C16" s="2">
         <v>0.08</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>0.08</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <f>8/7</f>
         <v>1.1428571428571428</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>0.08</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="2">
         <v>0.08</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>1.36</v>
       </c>
       <c r="I16" t="s">
@@ -1132,26 +1082,26 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="3">
+        <v>31</v>
+      </c>
+      <c r="C17" s="2">
         <f>1.5/7</f>
         <v>0.21428571428571427</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <f>1.5/7</f>
         <v>0.21428571428571427</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>0.42</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>0.32</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="2">
         <v>0.32</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="2">
         <v>0.64</v>
       </c>
       <c r="I17" t="s">
@@ -1160,27 +1110,27 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="3">
+        <v>45</v>
+      </c>
+      <c r="C18" s="2">
         <v>0.92</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <v>0.92</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>2.81</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>1.36</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="2">
         <v>1.36</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="2">
         <v>3.92</v>
       </c>
       <c r="I18" t="s">
@@ -1192,24 +1142,24 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="3">
+        <v>35</v>
+      </c>
+      <c r="C19" s="2">
         <v>27</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>27</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>27</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>32.5</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="2">
         <v>32.5</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="2">
         <v>32.5</v>
       </c>
       <c r="I19" t="s">
@@ -1218,20 +1168,20 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="3">
+        <v>34</v>
+      </c>
+      <c r="C20" s="2">
         <f>120/4</f>
         <v>30</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="2">
         <f>120/4</f>
         <v>30</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <f>125/4</f>
         <v>31.25</v>
       </c>
@@ -1248,25 +1198,25 @@
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="3">
+        <v>36</v>
+      </c>
+      <c r="C21" s="2">
         <f>120/9</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <f>120/9</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <f>125/9</f>
         <v>13.888888888888889</v>
       </c>
@@ -1283,7 +1233,7 @@
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1309,19 +1259,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1329,13 +1279,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <f>D2*0.8</f>
         <v>80</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>100</v>
       </c>
       <c r="E2" t="s">
@@ -1347,13 +1297,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3">
         <f t="shared" ref="C3:C21" si="0">D3*0.8</f>
         <v>80</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>100</v>
       </c>
       <c r="E3" t="s">
@@ -1365,13 +1315,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>50</v>
       </c>
       <c r="E4" t="s">
@@ -1383,13 +1333,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>100</v>
       </c>
       <c r="E5" t="s">
@@ -1398,44 +1348,44 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <f t="shared" si="0"/>
         <v>120.80000000000001</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <f t="shared" si="0"/>
         <v>39.200000000000003</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -1443,20 +1393,20 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <f t="shared" si="0"/>
         <v>395.32800000000003</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>494.16</v>
       </c>
       <c r="E8" t="s">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -1464,13 +1414,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" t="s">
@@ -1482,13 +1432,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C10">
         <f t="shared" si="0"/>
         <v>200</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>250</v>
       </c>
       <c r="E10" t="s">
@@ -1500,13 +1450,13 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <f t="shared" si="0"/>
         <v>11.200000000000001</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>14</v>
       </c>
       <c r="E11" t="s">
@@ -1518,13 +1468,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C12">
         <f t="shared" si="0"/>
         <v>23.200000000000003</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>29</v>
       </c>
       <c r="E12" t="s">
@@ -1536,13 +1486,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13">
         <f t="shared" si="0"/>
         <v>10.4</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>13</v>
       </c>
       <c r="E13" t="s">
@@ -1554,13 +1504,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C14">
         <f t="shared" si="0"/>
         <v>22.400000000000002</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>28</v>
       </c>
       <c r="E14" t="s">
@@ -1569,16 +1519,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="2">
         <v>50</v>
       </c>
       <c r="E15" t="s">
@@ -1587,16 +1537,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>25</v>
       </c>
       <c r="E16" t="s">
@@ -1608,34 +1558,34 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <f t="shared" si="0"/>
         <v>114.4</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="2">
         <v>143</v>
       </c>
       <c r="E17" t="s">
         <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <f t="shared" si="0"/>
         <v>134.4</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="2">
         <f>SUM(D16, D17)</f>
         <v>168</v>
       </c>
@@ -1648,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C19">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="2">
         <v>40</v>
       </c>
       <c r="E19" t="s">
@@ -1663,10 +1613,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <f t="shared" si="0"/>
@@ -1681,283 +1631,20 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="5">
+        <v>36</v>
+      </c>
+      <c r="C21" s="4">
         <f t="shared" si="0"/>
         <v>9.4400000000000013</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>11.8</v>
       </c>
       <c r="E21" t="s">
         <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DF08AA8-7AD0-5746-B43D-5FC654D3BAE9}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2">
-        <f>SUM(B3, B4)</f>
-        <v>0.91514773924053405</v>
-      </c>
-      <c r="C2">
-        <f>B2/B2</f>
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>0.70423595710256304</v>
-      </c>
-      <c r="C3">
-        <f>B3/B2</f>
-        <v>0.76953253218654816</v>
-      </c>
-      <c r="D3" s="6">
-        <f>C3*D2</f>
-        <v>1.5390650643730963</v>
-      </c>
-      <c r="E3" s="6">
-        <f>C3*E2</f>
-        <v>1.9238313304663703</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4">
-        <v>0.21091178213797099</v>
-      </c>
-      <c r="C4">
-        <f>B4/B2</f>
-        <v>0.23046746781345182</v>
-      </c>
-      <c r="D4" s="6">
-        <f>C4*D2</f>
-        <v>0.46093493562690363</v>
-      </c>
-      <c r="E4" s="6">
-        <f>C4*E2</f>
-        <v>0.57616866953362955</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB7421EB-7F73-F445-B679-99764E976302}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2">
-        <v>0.59656346217973899</v>
-      </c>
-      <c r="C2">
-        <f>B2/B5</f>
-        <v>0.1286421236117064</v>
-      </c>
-      <c r="D2" s="6">
-        <f>C2*D5</f>
-        <v>0.47726227859943077</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3">
-        <v>1.8310689663084301</v>
-      </c>
-      <c r="C3">
-        <f>B3/B5</f>
-        <v>0.39484919080484804</v>
-      </c>
-      <c r="D3" s="6">
-        <f>C3*D5</f>
-        <v>1.4648904978859862</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4">
-        <v>2.20975574134963</v>
-      </c>
-      <c r="C4">
-        <f>B4/B5</f>
-        <v>0.47650868558344567</v>
-      </c>
-      <c r="D4" s="6">
-        <f>C4*D5</f>
-        <v>1.7678472235145835</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5">
-        <f>SUM(B2:B4)</f>
-        <v>4.6373881698377986</v>
-      </c>
-      <c r="C5">
-        <f>B5/B5</f>
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>3.71</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02BFC3EC-6551-C84B-AC5D-CE47BD5A7DF8}">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2">
-        <f>SUM(B3:B4)</f>
-        <v>0.84846320275810294</v>
-      </c>
-      <c r="C2">
-        <f>B2/B2</f>
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>0.71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3">
-        <v>0.74767782400131699</v>
-      </c>
-      <c r="C3">
-        <f>B3/B2</f>
-        <v>0.88121420183083665</v>
-      </c>
-      <c r="D3" s="2">
-        <f>C3*D2</f>
-        <v>0.62566208329989403</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4">
-        <v>0.100785378756786</v>
-      </c>
-      <c r="C4">
-        <f>B4/B2</f>
-        <v>0.11878579816916343</v>
-      </c>
-      <c r="D4" s="2">
-        <f>C4*D2</f>
-        <v>8.4337916700106028E-2</v>
       </c>
     </row>
   </sheetData>
